--- a/Mediciones/RNA/T/RUN3_T_2NO_COM.xlsx
+++ b/Mediciones/RNA/T/RUN3_T_2NO_COM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340F5E0F-9EAE-48AC-A1D6-86CCC8311914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414C6E58-BEA3-41BD-B949-B10725C49487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuracion" sheetId="1" r:id="rId1"/>
@@ -40563,18 +40563,14 @@
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="I2" s="1"/>
       <c r="J2">
         <v>120</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
-      <c r="L2" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="L2" s="1"/>
       <c r="M2" t="s">
         <v>780</v>
       </c>
@@ -40670,18 +40666,14 @@
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3">
         <v>120</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="M3" t="s">
         <v>780</v>
       </c>
@@ -40777,18 +40769,14 @@
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4">
         <v>120</v>
       </c>
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="L4" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="L4" s="1"/>
       <c r="M4" t="s">
         <v>780</v>
       </c>
@@ -40884,18 +40872,14 @@
       <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5">
         <v>120</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="L5" s="1"/>
       <c r="M5" t="s">
         <v>780</v>
       </c>
@@ -40991,18 +40975,14 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="J6">
         <v>120</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
-      <c r="L6" s="1">
-        <v>0.98329999999999995</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="M6" t="s">
         <v>780</v>
       </c>
@@ -41098,18 +41078,14 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="1">
-        <v>0.97499999999999998</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7">
         <v>120</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
-      <c r="L7" s="1">
-        <v>0.97499999999999998</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="M7" t="s">
         <v>780</v>
       </c>
